--- a/reponsevie/lambda_scan/lambda_0.10/MSD_C.xlsx
+++ b/reponsevie/lambda_scan/lambda_0.10/MSD_C.xlsx
@@ -1,29 +1,79 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\2A\TP modelisation\modelisation-2A\reponsevie\lambda_scan\lambda_0.10\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E46FCE1A-1216-4C4D-9B2B-B6BC3A4330FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="840" yWindow="2010" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>t</t>
+  </si>
+  <si>
+    <t>run_1</t>
+  </si>
+  <si>
+    <t>run_2</t>
+  </si>
+  <si>
+    <t>run_3</t>
+  </si>
+  <si>
+    <t>run_4</t>
+  </si>
+  <si>
+    <t>run_5</t>
+  </si>
+  <si>
+    <t>run_moy</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -66,6 +116,1101 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="fr-FR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>run_moy</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="3.5612860892388451E-2"/>
+                  <c:y val="0.19865740740740739"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="fr-FR"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Feuil1!$A$2:$A$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>12.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Feuil1!$G$2:$G$26</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="25"/>
+                <c:pt idx="0">
+                  <c:v>1.6728656000000002</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.8658134</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.0561958000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.2311306000000002</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.4229659999999997</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5016166000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.6301695999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.7093088000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.8203971999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.8582776000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.9949186000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3.0574067999999999</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3.0805948000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.1395337999999997</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.1625190000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.1708398000000004</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.1930190000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.2908511999999996</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.3812693999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.5123607999999997</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.5915585999999999</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3.7918971999999997</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>3.8539363999999998</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3.8961736</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.1365293999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-74F1-44C3-9298-E546F914C276}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1556435552"/>
+        <c:axId val="1556436800"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1556435552"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1556436800"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1556436800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="fr-FR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1556435552"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="fr-FR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55AF5F45-2C78-4F80-A5EF-8B2B339A02E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +1475,636 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>0.5</v>
+      </c>
+      <c r="B2">
+        <v>1.5032970000000001</v>
+      </c>
+      <c r="C2">
+        <v>1.2104999999999999</v>
+      </c>
+      <c r="D2">
+        <v>1.903675</v>
+      </c>
+      <c r="E2">
+        <v>1.7800659999999999</v>
+      </c>
+      <c r="F2">
+        <v>1.96679</v>
+      </c>
+      <c r="G2">
+        <f>AVERAGE(B2:F2)</f>
+        <v>1.6728656000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1.722699</v>
+      </c>
+      <c r="C3">
+        <v>1.5920399999999999</v>
+      </c>
+      <c r="D3">
+        <v>1.945039</v>
+      </c>
+      <c r="E3">
+        <v>1.9667289999999999</v>
+      </c>
+      <c r="F3">
+        <v>2.10256</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G26" si="0">AVERAGE(B3:F3)</f>
+        <v>1.8658134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1.5</v>
+      </c>
+      <c r="B4">
+        <v>2.1377999999999999</v>
+      </c>
+      <c r="C4">
+        <v>1.6380319999999999</v>
+      </c>
+      <c r="D4">
+        <v>2.2300810000000002</v>
+      </c>
+      <c r="E4">
+        <v>2.0536880000000002</v>
+      </c>
+      <c r="F4">
+        <v>2.2213780000000001</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>2.0561958000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>2.3741680000000001</v>
+      </c>
+      <c r="C5">
+        <v>1.80891</v>
+      </c>
+      <c r="D5">
+        <v>2.4166340000000002</v>
+      </c>
+      <c r="E5">
+        <v>2.280491</v>
+      </c>
+      <c r="F5">
+        <v>2.2754500000000002</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>2.2311306000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2.5</v>
+      </c>
+      <c r="B6">
+        <v>2.6166800000000001</v>
+      </c>
+      <c r="C6">
+        <v>1.9564969999999999</v>
+      </c>
+      <c r="D6">
+        <v>2.5085839999999999</v>
+      </c>
+      <c r="E6">
+        <v>2.4418229999999999</v>
+      </c>
+      <c r="F6">
+        <v>2.5912459999999999</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>2.4229659999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>2.7651210000000002</v>
+      </c>
+      <c r="C7">
+        <v>2.0450689999999998</v>
+      </c>
+      <c r="D7">
+        <v>2.593045</v>
+      </c>
+      <c r="E7">
+        <v>2.4415659999999999</v>
+      </c>
+      <c r="F7">
+        <v>2.6632820000000001</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>2.5016166000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>3.5</v>
+      </c>
+      <c r="B8">
+        <v>3.0045139999999999</v>
+      </c>
+      <c r="C8">
+        <v>2.2111070000000002</v>
+      </c>
+      <c r="D8">
+        <v>2.6548600000000002</v>
+      </c>
+      <c r="E8">
+        <v>2.5250659999999998</v>
+      </c>
+      <c r="F8">
+        <v>2.7553010000000002</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>2.6301695999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>3.11971</v>
+      </c>
+      <c r="C9">
+        <v>2.397472</v>
+      </c>
+      <c r="D9">
+        <v>2.7351930000000002</v>
+      </c>
+      <c r="E9">
+        <v>2.574427</v>
+      </c>
+      <c r="F9">
+        <v>2.7197420000000001</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>2.7093088000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>4.5</v>
+      </c>
+      <c r="B10">
+        <v>3.3097479999999999</v>
+      </c>
+      <c r="C10">
+        <v>2.5964079999999998</v>
+      </c>
+      <c r="D10">
+        <v>2.7399849999999999</v>
+      </c>
+      <c r="E10">
+        <v>2.6545540000000001</v>
+      </c>
+      <c r="F10">
+        <v>2.801291</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>2.8203971999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>3.4614829999999999</v>
+      </c>
+      <c r="C11">
+        <v>2.8461110000000001</v>
+      </c>
+      <c r="D11">
+        <v>2.6268210000000001</v>
+      </c>
+      <c r="E11">
+        <v>2.6143160000000001</v>
+      </c>
+      <c r="F11">
+        <v>2.7426569999999999</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>2.8582776000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>5.5</v>
+      </c>
+      <c r="B12">
+        <v>3.5028260000000002</v>
+      </c>
+      <c r="C12">
+        <v>3.01979</v>
+      </c>
+      <c r="D12">
+        <v>2.6651829999999999</v>
+      </c>
+      <c r="E12">
+        <v>2.818962</v>
+      </c>
+      <c r="F12">
+        <v>2.967832</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>2.9949186000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>3.5820859999999999</v>
+      </c>
+      <c r="C13">
+        <v>3.1527080000000001</v>
+      </c>
+      <c r="D13">
+        <v>2.7581120000000001</v>
+      </c>
+      <c r="E13">
+        <v>2.9936769999999999</v>
+      </c>
+      <c r="F13">
+        <v>2.8004509999999998</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>3.0574067999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>6.5</v>
+      </c>
+      <c r="B14">
+        <v>3.5684269999999998</v>
+      </c>
+      <c r="C14">
+        <v>3.3720189999999999</v>
+      </c>
+      <c r="D14">
+        <v>2.6738430000000002</v>
+      </c>
+      <c r="E14">
+        <v>3.0335559999999999</v>
+      </c>
+      <c r="F14">
+        <v>2.7551290000000002</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>3.0805948000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>3.6647590000000001</v>
+      </c>
+      <c r="C15">
+        <v>3.4357449999999998</v>
+      </c>
+      <c r="D15">
+        <v>2.8214139999999999</v>
+      </c>
+      <c r="E15">
+        <v>3.1326320000000001</v>
+      </c>
+      <c r="F15">
+        <v>2.643119</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>3.1395337999999997</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>7.5</v>
+      </c>
+      <c r="B16">
+        <v>3.7141989999999998</v>
+      </c>
+      <c r="C16">
+        <v>3.334714</v>
+      </c>
+      <c r="D16">
+        <v>2.6109309999999999</v>
+      </c>
+      <c r="E16">
+        <v>3.31473</v>
+      </c>
+      <c r="F16">
+        <v>2.8380209999999999</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>3.1625190000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>3.8913820000000001</v>
+      </c>
+      <c r="C17">
+        <v>3.3718080000000001</v>
+      </c>
+      <c r="D17">
+        <v>2.4948459999999999</v>
+      </c>
+      <c r="E17">
+        <v>3.2204890000000002</v>
+      </c>
+      <c r="F17">
+        <v>2.8756740000000001</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>3.1708398000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>8.5</v>
+      </c>
+      <c r="B18">
+        <v>4.0273199999999996</v>
+      </c>
+      <c r="C18">
+        <v>3.3525040000000002</v>
+      </c>
+      <c r="D18">
+        <v>2.5402670000000001</v>
+      </c>
+      <c r="E18">
+        <v>3.1970079999999998</v>
+      </c>
+      <c r="F18">
+        <v>2.8479960000000002</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>3.1930190000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>4.0934739999999996</v>
+      </c>
+      <c r="C19">
+        <v>3.3523179999999999</v>
+      </c>
+      <c r="D19">
+        <v>2.6937899999999999</v>
+      </c>
+      <c r="E19">
+        <v>3.2856779999999999</v>
+      </c>
+      <c r="F19">
+        <v>3.0289959999999998</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>3.2908511999999996</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>9.5</v>
+      </c>
+      <c r="B20">
+        <v>4.1120559999999999</v>
+      </c>
+      <c r="C20">
+        <v>3.4039489999999999</v>
+      </c>
+      <c r="D20">
+        <v>2.8435830000000002</v>
+      </c>
+      <c r="E20">
+        <v>3.2337660000000001</v>
+      </c>
+      <c r="F20">
+        <v>3.3129930000000001</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>3.3812693999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>4.1171119999999997</v>
+      </c>
+      <c r="C21">
+        <v>3.5026630000000001</v>
+      </c>
+      <c r="D21">
+        <v>2.9449990000000001</v>
+      </c>
+      <c r="E21">
+        <v>3.3820670000000002</v>
+      </c>
+      <c r="F21">
+        <v>3.6149629999999999</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>3.5123607999999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>10.5</v>
+      </c>
+      <c r="B22">
+        <v>4.0637790000000003</v>
+      </c>
+      <c r="C22">
+        <v>3.5393560000000002</v>
+      </c>
+      <c r="D22">
+        <v>2.9407380000000001</v>
+      </c>
+      <c r="E22">
+        <v>3.5558179999999999</v>
+      </c>
+      <c r="F22">
+        <v>3.8581020000000001</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>3.5915585999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>4.1829720000000004</v>
+      </c>
+      <c r="C23">
+        <v>3.5094970000000001</v>
+      </c>
+      <c r="D23">
+        <v>3.2294969999999998</v>
+      </c>
+      <c r="E23">
+        <v>3.8877519999999999</v>
+      </c>
+      <c r="F23">
+        <v>4.1497679999999999</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>3.7918971999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>11.5</v>
+      </c>
+      <c r="B24">
+        <v>4.0645420000000003</v>
+      </c>
+      <c r="C24">
+        <v>3.3614060000000001</v>
+      </c>
+      <c r="D24">
+        <v>3.6047150000000001</v>
+      </c>
+      <c r="E24">
+        <v>4.009836</v>
+      </c>
+      <c r="F24">
+        <v>4.2291829999999999</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>3.8539363999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>3.9962879999999998</v>
+      </c>
+      <c r="C25">
+        <v>3.1918000000000002</v>
+      </c>
+      <c r="D25">
+        <v>3.975425</v>
+      </c>
+      <c r="E25">
+        <v>4.2205789999999999</v>
+      </c>
+      <c r="F25">
+        <v>4.0967760000000002</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>3.8961736</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>12.5</v>
+      </c>
+      <c r="B26">
+        <v>4.310149</v>
+      </c>
+      <c r="C26">
+        <v>3.4601679999999999</v>
+      </c>
+      <c r="D26">
+        <v>3.8297639999999999</v>
+      </c>
+      <c r="E26">
+        <v>4.1751659999999999</v>
+      </c>
+      <c r="F26">
+        <v>4.9074</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>4.1365293999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>